--- a/stories/arbres/TREE-SEC-018.xlsx
+++ b/stories/arbres/TREE-SEC-018.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Inès est dans la cuisine avec Papa. Papa est l'accompagnant. Inès reste avec l'accompagnant. Ses pieds restent à côté de Papa. Sa main tient la main de Papa. Maman verse l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1489,6 +1511,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -1657,6 +1684,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès choisit le bol rouge. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le ballon rouge. L'eau coule. Inès pose le ballon rouge près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2599,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2770,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Ça sent le pain. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2937,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3108,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. Le bois de la table est lisse. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3275,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3446,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. Un oiseau chante dehors. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3613,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3784,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le seau bleu. La cuillère tinte. Inès pose le seau bleu près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3975,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4146,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Le bois de la table est lisse. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4313,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4484,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. Un oiseau chante dehors. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4651,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4822,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. Le bol est tiède. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4989,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5160,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le doudou. Ça sent le pain. Inès pose le doudou près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5351,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5522,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Un oiseau chante dehors. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5689,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5860,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. Le bol est tiède. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6027,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6198,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. L'eau coule. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6365,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6369,6 +6536,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Inès choisit le bol bleu. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6549,6 +6721,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -6721,6 +6898,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6907,6 +7089,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7073,6 +7260,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le ballon rouge. Le bois de la table est lisse. Inès pose le ballon rouge près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7259,6 +7451,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7425,6 +7622,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Le bois de la table est lisse. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7587,6 +7789,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7753,6 +7960,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. Un oiseau chante dehors. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7915,6 +8127,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8081,6 +8298,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. Le bol est tiède. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8243,6 +8465,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8409,6 +8636,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le seau bleu. Un oiseau chante dehors. Inès pose le seau bleu près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8595,6 +8827,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8761,6 +8998,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Un oiseau chante dehors. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8923,6 +9165,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9089,6 +9336,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. Le bol est tiède. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9251,6 +9503,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9417,6 +9674,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. L'eau coule. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9579,6 +9841,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9745,6 +10012,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le doudou. Le bol est tiède. Inès pose le doudou près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9931,6 +10203,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10097,6 +10374,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Le bol est tiède. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10259,6 +10541,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10425,6 +10712,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. L'eau coule. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10587,6 +10879,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10753,6 +11050,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. La cuillère tinte. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10915,6 +11217,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11081,6 +11388,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Inès choisit le bol vert. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11261,6 +11573,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
     </row>
@@ -11433,6 +11750,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11619,6 +11941,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11785,6 +12112,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le ballon rouge. L'eau coule. Inès pose le ballon rouge près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11971,6 +12303,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12137,6 +12474,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Un oiseau chante dehors. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12299,6 +12641,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12465,6 +12812,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. Le bol est tiède. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12627,6 +12979,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12793,6 +13150,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. L'eau coule. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12955,6 +13317,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13121,6 +13488,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le seau bleu. La cuillère tinte. Inès pose le seau bleu près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13307,6 +13679,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13473,6 +13850,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. Le bol est tiède. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13635,6 +14017,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13801,6 +14188,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. L'eau coule. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13963,6 +14355,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14129,6 +14526,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. La cuillère tinte. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14291,6 +14693,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14457,6 +14864,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a choisi le doudou. Ça sent le pain. Inès pose le doudou près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14643,6 +15055,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14809,6 +15226,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chat. L'eau coule. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14971,6 +15393,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15137,6 +15564,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit le chien. La cuillère tinte. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15299,6 +15731,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15465,6 +15902,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Inès voit la poule. Ça sent le pain. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15627,6 +16069,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15645,7 +16092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15662,6 +16109,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-018.xlsx
+++ b/stories/arbres/TREE-SEC-018.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Inès est dans la cuisine avec Papa. Papa est l'accompagnant. Inès reste avec l'accompagnant. Ses pieds restent à côté de Papa. Sa main tient la main de Papa. Maman verse l'eau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
           <t>narrateur|Inès choisit le bol rouge. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Inès a choisi le ballon rouge. L'eau coule. Inès pose le ballon rouge près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2602,6 +2614,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2775,6 +2792,7 @@
           <t>narrateur|Inès voit le chat. Ça sent le pain. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2942,6 +2960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3113,6 +3132,11 @@
           <t>narrateur|Inès voit le chien. Le bois de la table est lisse. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3280,6 +3304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3451,6 +3476,7 @@
           <t>narrateur|Inès voit la poule. Un oiseau chante dehors. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3618,6 +3644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3789,6 +3816,7 @@
           <t>narrateur|Inès a choisi le seau bleu. La cuillère tinte. Inès pose le seau bleu près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3978,6 +4006,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4151,6 +4184,7 @@
           <t>narrateur|Inès voit le chat. Le bois de la table est lisse. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4318,6 +4352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4489,6 +4524,11 @@
           <t>narrateur|Inès voit le chien. Un oiseau chante dehors. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4656,6 +4696,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4827,6 +4868,7 @@
           <t>narrateur|Inès voit la poule. Le bol est tiède. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4994,6 +5036,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5165,6 +5208,7 @@
           <t>narrateur|Inès a choisi le doudou. Ça sent le pain. Inès pose le doudou près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5354,6 +5398,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5527,6 +5576,7 @@
           <t>narrateur|Inès voit le chat. Un oiseau chante dehors. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5694,6 +5744,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5865,6 +5916,11 @@
           <t>narrateur|Inès voit le chien. Le bol est tiède. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6032,6 +6088,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6203,6 +6260,7 @@
           <t>narrateur|Inès voit la poule. L'eau coule. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6370,6 +6428,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6541,6 +6600,7 @@
           <t>narrateur|Inès choisit le bol bleu. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6728,6 +6788,7 @@
           <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6903,6 +6964,7 @@
           <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7094,6 +7156,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7265,6 +7328,7 @@
           <t>narrateur|Inès a choisi le ballon rouge. Le bois de la table est lisse. Inès pose le ballon rouge près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7454,6 +7518,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7627,6 +7696,7 @@
           <t>narrateur|Inès voit le chat. Le bois de la table est lisse. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7794,6 +7864,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7965,6 +8036,11 @@
           <t>narrateur|Inès voit le chien. Un oiseau chante dehors. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8132,6 +8208,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8303,6 +8380,7 @@
           <t>narrateur|Inès voit la poule. Le bol est tiède. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8470,6 +8548,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8641,6 +8720,7 @@
           <t>narrateur|Inès a choisi le seau bleu. Un oiseau chante dehors. Inès pose le seau bleu près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8830,6 +8910,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -9003,6 +9088,7 @@
           <t>narrateur|Inès voit le chat. Un oiseau chante dehors. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9170,6 +9256,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9341,6 +9428,11 @@
           <t>narrateur|Inès voit le chien. Le bol est tiède. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9508,6 +9600,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9679,6 +9772,7 @@
           <t>narrateur|Inès voit la poule. L'eau coule. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9846,6 +9940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10017,6 +10112,7 @@
           <t>narrateur|Inès a choisi le doudou. Le bol est tiède. Inès pose le doudou près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10206,6 +10302,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10379,6 +10480,7 @@
           <t>narrateur|Inès voit le chat. Le bol est tiède. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10546,6 +10648,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10717,6 +10820,11 @@
           <t>narrateur|Inès voit le chien. L'eau coule. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10884,6 +10992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11055,6 +11164,7 @@
           <t>narrateur|Inès voit la poule. La cuillère tinte. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11222,6 +11332,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11393,6 +11504,7 @@
           <t>narrateur|Inès choisit le bol vert. Elle reste avec l'accompagnant. Pieds à côté de Papa. Main dans la main de Papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11580,6 +11692,7 @@
           <t>narrateur|On reste avec qui ? L'accompagnant.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11755,6 +11868,7 @@
           <t>narrateur|Oui. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès retient : rester avec l'accompagnant. La main tient la main de Papa, l'accompagnant. On continue, avec Papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11946,6 +12060,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12117,6 +12232,7 @@
           <t>narrateur|Inès a choisi le ballon rouge. L'eau coule. Inès pose le ballon rouge près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12306,6 +12422,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12479,6 +12600,7 @@
           <t>narrateur|Inès voit le chat. Un oiseau chante dehors. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12646,6 +12768,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12817,6 +12940,11 @@
           <t>narrateur|Inès voit le chien. Le bol est tiède. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12984,6 +13112,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13155,6 +13284,7 @@
           <t>narrateur|Inès voit la poule. L'eau coule. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13322,6 +13452,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13493,6 +13624,7 @@
           <t>narrateur|Inès a choisi le seau bleu. La cuillère tinte. Inès pose le seau bleu près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13682,6 +13814,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13855,6 +13992,7 @@
           <t>narrateur|Inès voit le chat. Le bol est tiède. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14022,6 +14160,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14193,6 +14332,11 @@
           <t>narrateur|Inès voit le chien. L'eau coule. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14360,6 +14504,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14531,6 +14676,7 @@
           <t>narrateur|Inès voit la poule. La cuillère tinte. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14698,6 +14844,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14869,6 +15016,7 @@
           <t>narrateur|Inès a choisi le doudou. Ça sent le pain. Inès pose le doudou près de Papa. Elle reste avec l'accompagnant. La main tient la main de Papa, l'accompagnant. Maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15058,6 +15206,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15231,6 +15384,7 @@
           <t>narrateur|Inès voit le chat. L'eau coule. Le chat vient sous la table. Inès reste avec Papa, l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15398,6 +15552,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15569,6 +15724,11 @@
           <t>narrateur|Inès voit le chien. La cuillère tinte. Le chien pose la tête près du banc. Inès reste avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15736,6 +15896,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15907,6 +16068,7 @@
           <t>narrateur|Inès voit la poule. Ça sent le pain. La poule est dans le jardin. Inès reste dans la cuisine, avec l'accompagnant. On reste avec l'accompagnant. Les pieds restent à côté. La main tient la main de l'adulte. Inès dit merci à Papa. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16074,6 +16236,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16092,7 +16255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16116,6 +16279,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16317,6 +16494,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
